--- a/sampleprojects/CHIP/excel/CHIP.xlsx
+++ b/sampleprojects/CHIP/excel/CHIP.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <si>
     <t>DT: Compute Eligibility</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t/>
@@ -199,12 +202,21 @@
     <t>TABLE_NUMBER: 1020</t>
   </si>
   <si>
+    <t>For each client in the group, we need to calculate a group size (we only need to do this for applying clients)</t>
+  </si>
+  <si>
     <t>for all clients whose applying == true</t>
   </si>
   <si>
+    <t>We want to compare a client against every other client in the case, so we set up a local variable to point to ApplyingClient</t>
+  </si>
+  <si>
     <t>local entity ApplyingClient = client</t>
   </si>
   <si>
+    <t>Now consider the client in respect to all the other clients in the case (We need to consider all clients in the case, even if not applying)</t>
+  </si>
+  <si>
     <t>Are we consider the client themselves?</t>
   </si>
   <si>
@@ -214,19 +226,19 @@
     <t>Include ApplyingClient's parents</t>
   </si>
   <si>
-    <t>the client is the parent of ApplyingClient</t>
+    <t>is there relationship in case.relationships where (type == "parent" and source == client and target == ApplyingClient)</t>
   </si>
   <si>
     <t>Include ApplyingClient's siblings</t>
   </si>
   <si>
-    <t>the client is the sibling of ApplyingClient</t>
+    <t>is there relationship in case.relationships where (type == "sibling" and source == client and target == ApplyingClient)</t>
   </si>
   <si>
     <t>Include ApplyingClient's children</t>
   </si>
   <si>
-    <t>the client is the child of ApplyingClient</t>
+    <t>is there relationship in case.relationships where (type == "child" and source == client and target == ApplyingClient)</t>
   </si>
   <si>
     <t>Include the unborn children in some cases</t>
@@ -269,9 +281,15 @@
     <t>TABLE_NUMBER: 1030</t>
   </si>
   <si>
+    <t>FPL = the Federal Poverty Limit calculated for the number of people in this client's Income Group.</t>
+  </si>
+  <si>
     <t>local int FPL = FPL_Base + FPL_PerAdditionalPerson * (client.IncomeGroupCount - 1 )</t>
   </si>
   <si>
+    <t>FPL200 = 200 percent of the Federal Poverty Limit</t>
+  </si>
+  <si>
     <t>local int FPL200 = FPL * 2</t>
   </si>
   <si>
@@ -404,6 +422,9 @@
     <t>Note rejection reason; add "The System does not yet support Medicaid Applications" to client.notes</t>
   </si>
   <si>
+    <t>add "The System does not yet support Medicaid Applications" to the client.notes</t>
+  </si>
+  <si>
     <t>DT: Evaluate FOODSTAMPS Eligibilty</t>
   </si>
   <si>
@@ -416,6 +437,9 @@
     <t>Note rejection reason; add "The System does not yet support Food Stamp Applications" to client.notes</t>
   </si>
   <si>
+    <t>add "The System does not yet support Food Stamp Applications" to the client.notes</t>
+  </si>
+  <si>
     <t>DT: Evaluate Results</t>
   </si>
   <si>
@@ -513,6 +537,21 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Q Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Reference</t>
   </si>
   <si>
     <t>case</t>
@@ -1596,40 +1635,40 @@
         <v>13</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -1637,10 +1676,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -1655,40 +1694,40 @@
         <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1735,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -1714,40 +1753,40 @@
         <v>13</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1755,10 +1794,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -1770,52 +1809,52 @@
         <v>13</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1871,58 +1910,58 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -1930,58 +1969,58 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1989,58 +2028,58 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -2048,58 +2087,58 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2107,58 +2146,58 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -2166,67 +2205,67 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -2282,58 +2321,58 @@
         <v>1</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -2341,58 +2380,58 @@
         <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -2400,58 +2439,58 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -2459,58 +2498,58 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2541,7 +2580,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2587,7 +2626,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2610,7 +2649,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2661,10 +2700,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -2688,10 +2727,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -2797,58 +2836,58 @@
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -2856,67 +2895,67 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -2972,58 +3011,58 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3055,7 +3094,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3078,7 +3117,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3101,7 +3140,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3124,7 +3163,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3175,10 +3214,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -3202,10 +3241,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -3229,10 +3268,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -3338,10 +3377,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
@@ -3380,16 +3419,16 @@
         <v>13</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -3397,10 +3436,10 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>13</v>
@@ -3439,16 +3478,16 @@
         <v>13</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -3456,10 +3495,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>13</v>
@@ -3498,16 +3537,16 @@
         <v>13</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -3515,10 +3554,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
@@ -3557,16 +3596,16 @@
         <v>12</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -3574,25 +3613,25 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>12</v>
@@ -3616,16 +3655,16 @@
         <v>13</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -3633,10 +3672,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>13</v>
@@ -3675,25 +3714,25 @@
         <v>12</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
@@ -3749,58 +3788,58 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -3808,58 +3847,58 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -3867,58 +3906,58 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3951,7 +3990,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3974,7 +4013,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3997,7 +4036,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4020,7 +4059,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4071,10 +4110,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4098,10 +4137,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4125,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4234,13 +4273,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>13</v>
@@ -4264,28 +4303,28 @@
         <v>13</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4293,13 +4332,13 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
@@ -4323,28 +4362,28 @@
         <v>13</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -4352,16 +4391,16 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -4382,28 +4421,28 @@
         <v>13</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -4411,10 +4450,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>13</v>
@@ -4423,7 +4462,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>12</v>
@@ -4441,28 +4480,28 @@
         <v>13</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -4470,10 +4509,10 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>13</v>
@@ -4485,7 +4524,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>13</v>
@@ -4500,28 +4539,28 @@
         <v>13</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -4529,10 +4568,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>13</v>
@@ -4559,28 +4598,28 @@
         <v>13</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -4588,10 +4627,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>13</v>
@@ -4606,7 +4645,7 @@
         <v>13</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -4618,28 +4657,28 @@
         <v>13</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -4647,10 +4686,10 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>13</v>
@@ -4668,7 +4707,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>13</v>
@@ -4677,28 +4716,28 @@
         <v>13</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -4706,10 +4745,10 @@
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>13</v>
@@ -4736,28 +4775,28 @@
         <v>13</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -4765,10 +4804,10 @@
         <v>10</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>13</v>
@@ -4792,40 +4831,40 @@
         <v>13</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" s="4">
         <v>1</v>
@@ -4881,58 +4920,58 @@
         <v>1</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -4940,58 +4979,58 @@
         <v>2</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -4999,58 +5038,58 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -5058,58 +5097,58 @@
         <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -5117,67 +5156,67 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -5233,58 +5272,58 @@
         <v>1</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -5292,58 +5331,58 @@
         <v>2</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
@@ -5351,58 +5390,58 @@
         <v>3</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -5410,58 +5449,58 @@
         <v>4</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
@@ -5469,58 +5508,58 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
@@ -5528,58 +5567,58 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -5587,58 +5626,58 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
@@ -5646,58 +5685,58 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -5731,7 +5770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5777,7 +5816,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5800,7 +5839,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5851,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5960,67 +5999,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -6076,58 +6115,58 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -6135,58 +6174,58 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6217,7 +6256,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6263,7 +6302,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6286,7 +6325,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6337,10 +6376,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6446,67 +6485,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -6562,58 +6601,58 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -6621,58 +6660,58 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6703,7 +6742,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6749,7 +6788,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6772,7 +6811,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6823,10 +6862,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6932,67 +6971,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -7048,58 +7087,58 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -7107,58 +7146,58 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -7166,58 +7205,58 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -7225,58 +7264,58 @@
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -7284,58 +7323,58 @@
         <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -7343,58 +7382,58 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -7402,58 +7441,58 @@
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -7461,58 +7500,58 @@
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -7520,58 +7559,58 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -7579,58 +7618,58 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -7661,45 +7700,65 @@
     <col customWidth="true" max="5" min="5" width="18"/>
     <col customWidth="true" max="7" min="6" width="8"/>
     <col customWidth="true" max="8" min="8" width="55"/>
+    <col customWidth="true" max="9" min="9" width="8"/>
+    <col customWidth="true" max="10" min="10" width="30"/>
+    <col customWidth="true" max="11" min="11" width="16"/>
+    <col customWidth="true" max="12" min="12" width="30"/>
+    <col customWidth="true" max="13" min="13" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -7707,117 +7766,182 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>172</v>
+        <v>185</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>176</v>
+        <v>189</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>178</v>
+        <v>191</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -7825,559 +7949,879 @@
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>181</v>
+        <v>194</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>185</v>
+        <v>198</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>188</v>
+        <v>201</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>192</v>
+        <v>205</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="H14" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>196</v>
+        <v>209</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>199</v>
+        <v>212</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>203</v>
+        <v>216</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>207</v>
+        <v>220</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>209</v>
+        <v>222</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>212</v>
+        <v>225</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>214</v>
+        <v>227</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>216</v>
+        <v>229</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>217</v>
+        <v>230</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>171</v>
-      </c>
       <c r="H29" s="16" t="s">
-        <v>220</v>
+        <v>233</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -8385,559 +8829,879 @@
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>224</v>
+        <v>237</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>225</v>
+        <v>238</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>228</v>
+        <v>241</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>228</v>
+        <v>241</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>233</v>
+        <v>246</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>225</v>
+        <v>238</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>237</v>
+        <v>250</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>240</v>
+        <v>253</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>224</v>
+        <v>237</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>224</v>
+        <v>237</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>225</v>
+        <v>238</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>228</v>
+        <v>241</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>228</v>
+        <v>241</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>228</v>
+        <v>241</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>228</v>
+        <v>241</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>228</v>
+        <v>241</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>255</v>
+        <v>268</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>258</v>
+        <v>271</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>261</v>
+        <v>274</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>255</v>
+        <v>268</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>255</v>
+        <v>268</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -8945,117 +9709,182 @@
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>265</v>
+        <v>278</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>267</v>
+        <v>280</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>268</v>
+        <v>281</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>270</v>
+        <v>283</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -9063,143 +9892,223 @@
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>274</v>
+        <v>287</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>276</v>
+        <v>289</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>268</v>
+        <v>281</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>279</v>
+        <v>292</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>282</v>
+        <v>295</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M62" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -9207,117 +10116,182 @@
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>268</v>
+        <v>281</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>286</v>
+        <v>299</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>288</v>
+        <v>301</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -9325,239 +10299,379 @@
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>290</v>
+        <v>303</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>292</v>
+        <v>305</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>293</v>
+        <v>306</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M71" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>294</v>
+        <v>307</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M72" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>295</v>
+        <v>308</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M73" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>296</v>
+        <v>309</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K74" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M74" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>297</v>
+        <v>310</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M75" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>224</v>
+        <v>237</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K76" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M76" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>298</v>
+        <v>311</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M77" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
